--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -49,9 +49,7 @@
     </font>
     <font>
       <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
-      <color rgb="FF0563C1"/>
+      <color rgb="000563C1"/>
       <sz val="11"/>
       <u val="single"/>
     </font>
@@ -450,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -504,7 +502,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>00400A</t>
         </is>
@@ -546,7 +544,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>00401A</t>
         </is>
@@ -588,7 +586,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>00402A</t>
         </is>
@@ -630,7 +628,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>00403A</t>
         </is>
@@ -672,7 +670,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>00404A</t>
         </is>
@@ -714,7 +712,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>00405A</t>
         </is>
@@ -756,1008 +754,1050 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>00406A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>主動中信台灣收益</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>張書廷</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>合作金庫</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>月配</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.035%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>00407A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>凱基台灣主動式</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>趙偉志</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>彰化銀行</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>不配息</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>0.035%</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>不配息</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>00408A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>主動第一金優股息</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>張正中</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>臺灣中小企業銀行</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>季配 (1,4,7,10)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>0.035%</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>00980A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>野村臺灣智慧優選</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>游景德</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>華南銀行</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>季配 (2,5,8,11)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.035%</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>00981A</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>統一台股增長</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>陳釧瑤</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>彰化銀行</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>季配 (3,6,9,12)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>1.0%~1.2%</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>0.10%~0.12%</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>00982A</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>群益台灣精選強棒</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>陳沅易</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>中國信託</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>季配 (2,5,8,11)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>0.80%</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.035%</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>00983A</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>中信ARK創新</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>唐祖蔭</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>第一銀行</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>年配 (12)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>0.7%~1.0%</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>0.12%~0.15%</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>00984A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>安聯台灣高息成長</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>廖本隆</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>國泰世華</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>季配 (1,4,7,10)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>0.70%</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2026/07/15</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>00985A</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>野村臺灣增強50</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>林浩詳</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>台北富邦</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>年配 (12)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>0.45%</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>0.035%</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>00986A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>台新全球龍頭成長</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>蘇聖峰</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>臺灣企銀</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>年配 (10)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>1.00%</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0.25%</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>00987A</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>台新優勢成長</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>魏永祥</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>彰化銀行</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>年配 (11)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>00988A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>統一全球創新</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>陳意婷</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>元大銀行</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>年配 (10)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1.2%~1.4%</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.10%~0.12%</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>00989A</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>摩根大美國領先科技</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>蓋欣聖</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>中國信託</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>季配 (1,4,7,10)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>0.15%</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>00990A</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>元大AI新經濟</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>吳昭豪</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>臺灣銀行</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>不配息</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>0.90%</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>0.15%</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>不配息</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>00991A</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>復華台灣未來50</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>呂宏宇</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>第一銀行</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>半年配 (1,7)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>0.80%~1.0%</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>0.035%~0.04%</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2026/07/20</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>00992A</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>群益科技創新</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>陳朝政</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>第一銀行</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>季配 (1,4,7,10)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>1.0%~1.2%</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>2026/07/15</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>00993A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>安聯台灣主動</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>施政廷</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>中國信託</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>年配 (12)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>0.80%</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>00994A</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>第一金台股優</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>張正中</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>永豐商業銀行</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>季配 (3,6,9,12)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>0.70%</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>0.035%</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>2026/06/17</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>00995A</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>中信台灣卓越成長</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>張書廷</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>元大銀行</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>季配 (1,4,7,10)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>00996A</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>兆豐台灣豐收</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>王仲良</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>元大銀行</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>季配 (1,4,7,10)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>0.80%</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>00997A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>群益美國增長</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>吳承恕</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>第一銀行</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>季配 (1,4,7,10)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>1.0%~1.2%</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>0.1%~0.12%</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>2026/07/03</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>00998A</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>復華全球金融入息</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>張正宇</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>合作金庫</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>季配 (3,6,9,12)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>1.0%~1.2%</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>0.10%~0.14%</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2026/06/16</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>00999A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>野村臺灣策略高息</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>游景德</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>第一銀行</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>季配 (3,6,9,12)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>0.70%</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>0.035%</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>尚未公告</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>00980D</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>聯博投等債入息</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>陳俊憲</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>中國信託</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>月配</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>0.60%~0.65%</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>0.08%~0.12%</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2026/07/15</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>00983D</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>富邦複合收益</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>游陳達</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>第一銀行</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>月配</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>0.55%~0.65%</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>0.06%~0.10%</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2026/07/15</t>
         </is>
@@ -1765,6 +1805,39 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H33"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主動型" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,45 +13,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="槓桿反向" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海外型" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'主動型'!$A$1:$H$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'市值型'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'高股息'!$A$1:$I$22</definedName>
-  </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
-      <name val="新細明體"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
       <color rgb="000563C1"/>
-      <sz val="11"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -74,18 +54,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -449,14 +423,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="3" max="4"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="15" bestFit="1" customWidth="1" min="6" max="7"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,7 +478,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>00400A</t>
         </is>
@@ -544,7 +520,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>00401A</t>
         </is>
@@ -586,7 +562,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>00402A</t>
         </is>
@@ -628,7 +604,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>00403A</t>
         </is>
@@ -670,7 +646,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00404A</t>
         </is>
@@ -712,7 +688,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>00405A</t>
         </is>
@@ -754,7 +730,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>00406A</t>
         </is>
@@ -796,7 +772,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>00407A</t>
         </is>
@@ -838,7 +814,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>00408A</t>
         </is>
@@ -880,7 +856,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>00980A</t>
         </is>
@@ -922,7 +898,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>00981A</t>
         </is>
@@ -964,7 +940,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>00982A</t>
         </is>
@@ -1006,7 +982,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>00983A</t>
         </is>
@@ -1048,7 +1024,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>00984A</t>
         </is>
@@ -1090,7 +1066,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>00985A</t>
         </is>
@@ -1132,7 +1108,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>00986A</t>
         </is>
@@ -1174,7 +1150,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>00987A</t>
         </is>
@@ -1216,7 +1192,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>00988A</t>
         </is>
@@ -1258,7 +1234,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>00989A</t>
         </is>
@@ -1300,7 +1276,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>00990A</t>
         </is>
@@ -1342,7 +1318,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>00991A</t>
         </is>
@@ -1384,7 +1360,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>00992A</t>
         </is>
@@ -1426,7 +1402,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>00993A</t>
         </is>
@@ -1468,7 +1444,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>00994A</t>
         </is>
@@ -1510,7 +1486,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>00995A</t>
         </is>
@@ -1552,7 +1528,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>00996A</t>
         </is>
@@ -1594,7 +1570,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>00997A</t>
         </is>
@@ -1636,7 +1612,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>00998A</t>
         </is>
@@ -1678,7 +1654,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>00999A</t>
         </is>
@@ -1720,7 +1696,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>00980D</t>
         </is>
@@ -1762,7 +1738,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>00983D</t>
         </is>
@@ -1804,7 +1780,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H33"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -1839,7 +1814,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1850,16 +1824,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1952,7 +1927,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/20</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1974,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/04/17</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2021,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026/10/22</t>
+          <t>2025/10/22</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2068,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2115,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2162,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/04/17</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2209,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/05/21</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2256,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/01/19</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2303,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/24</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2350,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2397,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2444,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/02/26</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2491,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/15</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2538,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026/03/17</t>
+          <t>2026/03/16</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2585,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/02/25</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2632,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026/03/17</t>
+          <t>2026/03/16</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2679,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/14</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2778,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -2826,7 +2800,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -2837,16 +2810,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="24.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="31.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2939,7 +2913,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/20</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2960,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/01/19</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3007,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/06/18</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3101,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/05/19</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3148,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/05/18</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3195,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3242,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026/08/25</t>
+          <t>2026/06/23</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3289,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/15</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3336,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/17</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3383,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/15</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3430,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/07/20</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3477,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/24</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3524,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3571,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>不配息</t>
+          <t>2026/07/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3618,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/07/01</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3665,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/07/08</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3712,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3759,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/07/03</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3806,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3853,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -3919,14 +3892,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="18.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="30.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="15" bestFit="1" customWidth="1" min="6" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4397,18 +4371,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="29" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="33.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="20" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="15.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="20.85546875" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4452,11 +4425,6 @@
           <t>保管費 (年率)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>最近除息日期</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -4499,11 +4467,6 @@
           <t>0.06% (級距)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>不配息</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -4546,11 +4509,6 @@
           <t>0.16%~0.21%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>不配息</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4593,11 +4551,6 @@
           <t>0.08%~0.16%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026/06/17</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -4640,11 +4593,6 @@
           <t>0.18%</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>不配息</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -4687,11 +4635,6 @@
           <t>0.10%~0.15%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026/01/20</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -4734,11 +4677,6 @@
           <t>0.06%~0.11%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026/01/20</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -4781,11 +4719,6 @@
           <t>0.08%~0.15%</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>不配息</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -4828,162 +4761,142 @@
           <t>0.20%</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>不配息</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>009821</t>
+          <t>009823</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>野村全球稀土與關鍵資源</t>
+          <t>群益標普500 ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>張怡琳</t>
+          <t>標普 500 指數（S&amp;P 500 Index）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>永豐商業銀行</t>
+          <t>謝明志</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NYSE TIP全球稀土與關鍵資源指數</t>
+          <t>華南銀行</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>不配息</t>
+          <t>季配 (2,5,8,11)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.20% (級距)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>不配息</t>
+          <t>0.06%~0.10% (級距)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>009823</t>
+          <t>009824</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>群益標普500 ETF</t>
+          <t>群益美國科技巨頭ETF基金</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>標普 500 指數（S&amp;P 500 Index）</t>
+          <t>Solactive美國科技巨頭指數</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>謝明志</t>
+          <t>李晉含</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>華南銀行</t>
+          <t>中國信託商業銀行</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>季配 (2,5,8,11)</t>
+          <t>季配 (3,6,9,12)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.20% (級距)</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.06%~0.10% (級距)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>尚未除息</t>
+          <t>0.06%~0.12% (級距)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>009824</t>
+          <t>009821</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>群益美國科技巨頭ETF基金</t>
+          <t>野村全球稀土與關鍵資源</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Solactive美國科技巨頭指數</t>
+          <t>NYSE TIP全球稀土與關鍵資源指數</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>李晉含</t>
+          <t>張怡琳</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>中國信託商業銀行</t>
+          <t>永豐商業銀行</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>季配 (3,6,9,12)</t>
+          <t>不配息</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.06%~0.12% (級距)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>尚未除息</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>009826</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>貝萊德iShares安碩世界股票</t>
+          <t>貝萊德iShares未來世界股票</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4998,7 +4911,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>渣打銀行</t>
+          <t>華南商業銀行</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5008,17 +4921,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.40%~0.45%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.10%~0.15%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>不配息</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主動型" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,19 +13,34 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海外型" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -54,12 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -423,16 +438,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="20" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="15" bestFit="1" customWidth="1" min="6" max="7"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,7 +492,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>00400A</t>
         </is>
@@ -520,7 +534,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>00401A</t>
         </is>
@@ -562,7 +576,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>00402A</t>
         </is>
@@ -604,7 +618,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>00403A</t>
         </is>
@@ -646,7 +660,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>00404A</t>
         </is>
@@ -688,7 +702,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>00405A</t>
         </is>
@@ -730,7 +744,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>00406A</t>
         </is>
@@ -772,7 +786,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>00407A</t>
         </is>
@@ -814,7 +828,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>00408A</t>
         </is>
@@ -856,7 +870,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>00980A</t>
         </is>
@@ -898,7 +912,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>00981A</t>
         </is>
@@ -940,7 +954,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>00982A</t>
         </is>
@@ -982,7 +996,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>00983A</t>
         </is>
@@ -1024,7 +1038,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>00984A</t>
         </is>
@@ -1066,7 +1080,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>00985A</t>
         </is>
@@ -1108,7 +1122,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>00986A</t>
         </is>
@@ -1150,7 +1164,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>00987A</t>
         </is>
@@ -1192,7 +1206,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>00988A</t>
         </is>
@@ -1234,7 +1248,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>00989A</t>
         </is>
@@ -1276,7 +1290,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>00990A</t>
         </is>
@@ -1318,7 +1332,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>00991A</t>
         </is>
@@ -1360,7 +1374,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>00992A</t>
         </is>
@@ -1402,7 +1416,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>00993A</t>
         </is>
@@ -1444,7 +1458,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>00994A</t>
         </is>
@@ -1486,7 +1500,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>00995A</t>
         </is>
@@ -1528,7 +1542,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>00996A</t>
         </is>
@@ -1570,7 +1584,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>00997A</t>
         </is>
@@ -1612,7 +1626,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>00998A</t>
         </is>
@@ -1654,7 +1668,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>00999A</t>
         </is>
@@ -1696,7 +1710,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>00980D</t>
         </is>
@@ -1738,7 +1752,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>00983D</t>
         </is>
@@ -1824,16 +1838,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="5" max="6"/>
+    <col width="13" customWidth="1" min="7" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -2810,7 +2822,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2818,8 +2830,7 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -3892,15 +3903,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="6" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4372,7 +4382,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
@@ -41,6 +41,21 @@
       <charset val="136"/>
       <family val="3"/>
       <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -65,16 +80,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -492,7 +511,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>00400A</t>
         </is>
@@ -534,7 +553,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>00401A</t>
         </is>
@@ -576,7 +595,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>00402A</t>
         </is>
@@ -618,7 +637,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>00403A</t>
         </is>
@@ -660,7 +679,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>00404A</t>
         </is>
@@ -702,7 +721,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>00405A</t>
         </is>
@@ -744,7 +763,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>00406A</t>
         </is>
@@ -786,7 +805,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>00407A</t>
         </is>
@@ -828,7 +847,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>00408A</t>
         </is>
@@ -869,8 +888,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="11" ht="16.5" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>00980A</t>
         </is>
@@ -911,8 +930,8 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="12" ht="16.5" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>00981A</t>
         </is>
@@ -953,8 +972,8 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13" ht="16.5" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>00982A</t>
         </is>
@@ -996,7 +1015,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>00983A</t>
         </is>
@@ -1038,7 +1057,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>00984A</t>
         </is>
@@ -1080,7 +1099,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>00985A</t>
         </is>
@@ -1122,7 +1141,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>00986A</t>
         </is>
@@ -1164,7 +1183,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>00987A</t>
         </is>
@@ -1206,7 +1225,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>00988A</t>
         </is>
@@ -1248,7 +1267,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>00989A</t>
         </is>
@@ -1290,7 +1309,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>00990A</t>
         </is>
@@ -1332,7 +1351,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>00991A</t>
         </is>
@@ -1374,7 +1393,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>00992A</t>
         </is>
@@ -1416,7 +1435,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>00993A</t>
         </is>
@@ -1458,7 +1477,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>00994A</t>
         </is>
@@ -1500,7 +1519,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>00995A</t>
         </is>
@@ -1542,7 +1561,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>00996A</t>
         </is>
@@ -1584,7 +1603,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>00997A</t>
         </is>
@@ -1626,7 +1645,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>00998A</t>
         </is>
@@ -1668,7 +1687,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>00999A</t>
         </is>
@@ -1710,7 +1729,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>00980D</t>
         </is>
@@ -1752,7 +1771,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>00983D</t>
         </is>
